--- a/prep_and_checklists/Melio  /ORDER_GUIDE_Melio  _Thursday, January 15, 2026  _0.xlsx
+++ b/prep_and_checklists/Melio  /ORDER_GUIDE_Melio  _Thursday, January 15, 2026  _0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Melio  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3A177C-B450-8A4D-9A4E-3312A6C6A17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F270F298-A76F-2647-B39B-2139ACC98615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="1080" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -812,7 +812,8 @@
     <col min="6" max="6" width="28" style="2" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="22.83203125" style="2" customWidth="1"/>
-    <col min="9" max="10" width="18" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18" style="2" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
     <col min="13" max="25" width="8.83203125" style="2" customWidth="1"/>
@@ -2510,6 +2511,6 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="39" orientation="landscape"/>
 </worksheet>
 </file>